--- a/measurements/32/Filled_2D_sections/sagittal/week32_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/32/Filled_2D_sections/sagittal/week32_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AF27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,97 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +591,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.572278405710887</v>
+        <v>2886.394557823129</v>
       </c>
       <c r="D2" t="n">
-        <v>13.77174869688546</v>
+        <v>268.8769983677637</v>
       </c>
       <c r="E2" t="n">
-        <v>12.18261878664901</v>
+        <v>237.8511286917187</v>
       </c>
       <c r="F2" t="n">
         <v>1.130442389938195</v>
@@ -525,24 +610,54 @@
         <v>0.5017163552310837</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5980373475609756</v>
+        <v>1.296502976190476</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5980373475609756</v>
+        <v>11.67596726190476</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5980373475609756</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>4.707651289682539</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>11.67596726190476</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5.591517857142857</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.365699404761904</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.506696428571428</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.296502976190476</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>7.516463414634147</v>
+      <c r="AF2" s="2" t="n">
+        <v>2865.119047619047</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +668,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.572278405710887</v>
+        <v>2886.394557823129</v>
       </c>
       <c r="D3" t="n">
-        <v>13.77174869688546</v>
+        <v>268.8769983677637</v>
       </c>
       <c r="E3" t="n">
-        <v>12.18261878664901</v>
+        <v>237.8511286917187</v>
       </c>
       <c r="F3" t="n">
         <v>1.130442389938195</v>
@@ -572,24 +687,54 @@
         <v>0.5017163552310837</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5980373475609756</v>
+        <v>1.296502976190476</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5980373475609756</v>
+        <v>11.67596726190476</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5980373475609756</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>4.707651289682539</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>11.67596726190476</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.591517857142857</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.365699404761904</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.506696428571428</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.296502976190476</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>14.12809500388983</v>
+      <c r="AF3" s="2" t="n">
+        <v>275.83423579023</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +745,70 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.577334919690661</v>
+        <v>2888.321995464853</v>
       </c>
       <c r="D4" t="n">
-        <v>14.09055525791354</v>
+        <v>275.1013169402167</v>
       </c>
       <c r="E4" t="n">
-        <v>12.22894792440461</v>
+        <v>238.7556499526614</v>
       </c>
       <c r="F4" t="n">
         <v>1.152229557686956</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4795900151996347</v>
+        <v>0.4795900151996348</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5958460365853658</v>
+        <v>1.277901785714286</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5958460365853658</v>
+        <v>11.63318452380952</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5958460365853658</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>5.368923611111112</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.445684523809524</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11.63318452380952</v>
+      </c>
+      <c r="T4" t="n">
+        <v>6.961495535714286</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3.089657738095238</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.277901785714286</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>12.1588239413936</v>
+      <c r="AF4" s="2" t="n">
+        <v>237.3865626653035</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +819,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.594883997620465</v>
+        <v>2895.01133786848</v>
       </c>
       <c r="D5" t="n">
-        <v>14.64489476855208</v>
+        <v>285.9241359574454</v>
       </c>
       <c r="E5" t="n">
-        <v>12.44427540244126</v>
+        <v>242.9596626190912</v>
       </c>
       <c r="F5" t="n">
         <v>1.176837886895296</v>
@@ -666,23 +838,50 @@
         <v>0.4449984499172473</v>
       </c>
       <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.703869047619047</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12.82552083333333</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.235916241496598</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.6569169207317074</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.6569169207317074</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.6569169207317074</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>12.82552083333333</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.289434523809524</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7.475818452380952</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5.824404761904762</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.703869047619047</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AF5" s="2" t="n">
         <v>1.161704629572267</v>
       </c>
     </row>
@@ -694,17 +893,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.592801903628793</v>
+        <v>2894.21768707483</v>
       </c>
       <c r="D6" t="n">
-        <v>15.11841218064471</v>
+        <v>295.1689997173491</v>
       </c>
       <c r="E6" t="n">
-        <v>12.53591829392968</v>
+        <v>244.7488809767223</v>
       </c>
       <c r="F6" t="n">
         <v>1.206007555742092</v>
@@ -713,23 +912,47 @@
         <v>0.4174452946978577</v>
       </c>
       <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.259672619047619</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12.92782738095238</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.00015943877551</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.662157012195122</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.662157012195122</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.662157012195122</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>12.92782738095238</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4.259672619047619</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8.634672619047619</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6.012214781746031</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AF6" s="2" t="n">
         <v>0.4759142537537831</v>
       </c>
     </row>
@@ -741,17 +964,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.608863771564545</v>
+        <v>2900.340136054422</v>
       </c>
       <c r="D7" t="n">
-        <v>15.60968377532029</v>
+        <v>304.7604927562532</v>
       </c>
       <c r="E7" t="n">
-        <v>12.48958916780425</v>
+        <v>243.8443599428449</v>
       </c>
       <c r="F7" t="n">
         <v>1.249815631690995</v>
@@ -760,24 +983,48 @@
         <v>0.3924112615360085</v>
       </c>
       <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.942336309523809</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13.203125</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.326477465986394</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.6762576219512195</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.6762576219512195</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.6762576219512195</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>13.203125</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4.942336309523809</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8.502604166666666</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6.34703621031746</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.45</v>
+      <c r="AF7" s="2" t="n">
+        <v>6.95</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1035,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.53837001784652</v>
+        <v>2873.469387755102</v>
       </c>
       <c r="D8" t="n">
-        <v>15.77031271050616</v>
+        <v>307.8965814908345</v>
       </c>
       <c r="E8" t="n">
-        <v>12.57286268327294</v>
+        <v>245.4701761972336</v>
       </c>
       <c r="F8" t="n">
         <v>1.254313604449616</v>
@@ -807,24 +1054,48 @@
         <v>0.3808962567791273</v>
       </c>
       <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.942336309523809</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13.02641369047619</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.455888605442177</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.6672065548780488</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.6672065548780488</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.6672065548780488</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>13.02641369047619</v>
+      </c>
+      <c r="N8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4.942336309523809</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8.969494047619047</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6.527467757936509</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6108570460704608</v>
+      <c r="AF8" s="2" t="n">
+        <v>3.157924107142857</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1106,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.567221891731113</v>
+        <v>2884.467120181406</v>
       </c>
       <c r="D9" t="n">
-        <v>14.51774347119215</v>
+        <v>283.4416582470848</v>
       </c>
       <c r="E9" t="n">
-        <v>12.69654724656082</v>
+        <v>247.8849700519017</v>
       </c>
       <c r="F9" t="n">
         <v>1.143440274687644</v>
@@ -854,15 +1125,45 @@
         <v>0.4511781889135826</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.918154761904762</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.78784013605442</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4.918154761904762</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6.78784013605442</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.6108570460704608</v>
+      <c r="AF9" s="2" t="n">
+        <v>10.40541294642857</v>
       </c>
     </row>
     <row r="10">
@@ -873,34 +1174,64 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.547888161808448</v>
+        <v>2877.097505668934</v>
       </c>
       <c r="D10" t="n">
-        <v>14.39752561871599</v>
+        <v>281.0945477939787</v>
       </c>
       <c r="E10" t="n">
-        <v>12.65368481670938</v>
+        <v>247.0481321357545</v>
       </c>
       <c r="F10" t="n">
         <v>1.13781288433104</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4575721681431438</v>
+        <v>0.4575721681431439</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.893973214285714</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.666400935374149</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4.893973214285714</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6.666400935374149</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.6108570460704608</v>
+      <c r="AF10" s="2" t="n">
+        <v>5.992301543013038</v>
       </c>
     </row>
     <row r="11">
@@ -911,26 +1242,64 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.554431885782273</v>
+        <v>2879.591836734694</v>
       </c>
       <c r="D11" t="n">
-        <v>14.17036201023474</v>
+        <v>276.6594487712497</v>
       </c>
       <c r="E11" t="n">
-        <v>12.41223371610409</v>
+        <v>242.3340868382227</v>
       </c>
       <c r="F11" t="n">
         <v>1.141644794510241</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4727698616544777</v>
+        <v>0.4727698616544776</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.4140625</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.695808531746032</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4.4140625</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6.695808531746032</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -941,26 +1310,67 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.64098750743605</v>
+        <v>2912.585034013605</v>
       </c>
       <c r="D12" t="n">
-        <v>14.23342993782788</v>
+        <v>277.8907749766395</v>
       </c>
       <c r="E12" t="n">
-        <v>12.3432476898519</v>
+        <v>240.9872168018704</v>
       </c>
       <c r="F12" t="n">
         <v>1.153134920036483</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4739583924440207</v>
+        <v>0.4739583924440209</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.679315476190476</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9.047619047619047</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6.533358134920634</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4.68563988095238</v>
+      </c>
+      <c r="S12" t="n">
+        <v>9.047619047619047</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7.104166666666666</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.679315476190476</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="n">
+        <v>12.99572172619047</v>
       </c>
     </row>
     <row r="13">
@@ -971,26 +1381,70 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7.702558001189768</v>
+        <v>2936.054421768707</v>
       </c>
       <c r="D13" t="n">
-        <v>13.73277358020224</v>
+        <v>268.1160556134723</v>
       </c>
       <c r="E13" t="n">
-        <v>12.1732339539179</v>
+        <v>237.6679010050637</v>
       </c>
       <c r="F13" t="n">
-        <v>1.128112187130226</v>
+        <v>1.128112187130225</v>
       </c>
       <c r="G13" t="n">
-        <v>0.51324924830628</v>
+        <v>0.5132492483062802</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.519345238095238</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8.400297619047619</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.829081632653062</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.564732142857142</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8.400297619047619</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6.730654761904762</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3.630952380952381</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.519345238095238</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>5.35</v>
       </c>
     </row>
     <row r="14">
@@ -1001,26 +1455,73 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.720404521118382</v>
+        <v>2942.857142857143</v>
       </c>
       <c r="D14" t="n">
-        <v>13.74114300565022</v>
+        <v>268.2794586817423</v>
       </c>
       <c r="E14" t="n">
-        <v>12.13282290900626</v>
+        <v>236.8789234615508</v>
       </c>
       <c r="F14" t="n">
         <v>1.132559430621055</v>
       </c>
       <c r="G14" t="n">
-        <v>0.513811951132811</v>
+        <v>0.5138119511328111</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.363467261904762</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8.508184523809524</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.16903831845238</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>4.600074404761904</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8.508184523809524</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6.574032738095238</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.597470238095238</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.521205357142857</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.363467261904762</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>11.67596726190476</v>
       </c>
     </row>
     <row r="15">
@@ -1031,26 +1532,67 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.570791195716835</v>
+        <v>2885.827664399093</v>
       </c>
       <c r="D15" t="n">
-        <v>13.65786950471925</v>
+        <v>266.6536427111853</v>
       </c>
       <c r="E15" t="n">
-        <v>11.95443975925446</v>
+        <v>233.3962048235394</v>
       </c>
       <c r="F15" t="n">
         <v>1.142493481900404</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5100176603258449</v>
+        <v>0.5100176603258448</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.431919642857143</v>
+      </c>
+      <c r="J15" t="n">
+        <v>9.071800595238095</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.875584608843538</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.789806547619047</v>
+      </c>
+      <c r="S15" t="n">
+        <v>9.071800595238095</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6.282862103174604</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3.431919642857143</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>5.591517857142857</v>
       </c>
     </row>
     <row r="16">
@@ -1061,26 +1603,67 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.556216537775134</v>
+        <v>2880.272108843537</v>
       </c>
       <c r="D16" t="n">
-        <v>13.46519890645655</v>
+        <v>262.891978649866</v>
       </c>
       <c r="E16" t="n">
-        <v>11.87361762291048</v>
+        <v>231.8182488282521</v>
       </c>
       <c r="F16" t="n">
-        <v>1.134043501659938</v>
+        <v>1.134043501659939</v>
       </c>
       <c r="G16" t="n">
         <v>0.523707402600031</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.630208333333333</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9.034598214285714</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.610119047619048</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.618675595238095</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9.034598214285714</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6.106770833333333</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.630208333333333</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>4.365699404761904</v>
       </c>
     </row>
     <row r="17">
@@ -1091,17 +1674,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.506543723973826</v>
+        <v>2861.337868480725</v>
       </c>
       <c r="D17" t="n">
-        <v>13.64603338590482</v>
+        <v>266.4225565819513</v>
       </c>
       <c r="E17" t="n">
-        <v>11.82483712347542</v>
+        <v>230.8658676488059</v>
       </c>
       <c r="F17" t="n">
         <v>1.154014490298039</v>
@@ -1110,7 +1693,48 @@
         <v>0.5065671506539673</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.439360119047619</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8.999255952380953</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.836522108843537</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.002976190476191</v>
+      </c>
+      <c r="S17" t="n">
+        <v>8.999255952380953</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6.236049107142857</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3.439360119047619</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="n">
+        <v>4.625599371693122</v>
       </c>
     </row>
     <row r="18">
@@ -1121,26 +1745,67 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.43634741225461</v>
+        <v>2834.580498866213</v>
       </c>
       <c r="D18" t="n">
-        <v>13.74359434697686</v>
+        <v>268.3273182028815</v>
       </c>
       <c r="E18" t="n">
-        <v>11.76768723348292</v>
+        <v>229.7500840822856</v>
       </c>
       <c r="F18" t="n">
         <v>1.16790955387324</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4947307203503362</v>
+        <v>0.4947307203503364</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.610491071428571</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9.497767857142856</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.018548044217686</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.590773809523809</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9.497767857142856</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6.419890873015873</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3.610491071428571</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>9.242001488095237</v>
       </c>
     </row>
     <row r="19">
@@ -1151,26 +1816,70 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.343842950624628</v>
+        <v>2799.319727891156</v>
       </c>
       <c r="D19" t="n">
-        <v>13.51397938263126</v>
+        <v>263.8443593751816</v>
       </c>
       <c r="E19" t="n">
-        <v>11.64400265565733</v>
+        <v>227.3352899437859</v>
       </c>
       <c r="F19" t="n">
         <v>1.160595697396667</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5053202947852521</v>
+        <v>0.505320294785252</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.322172619047619</v>
+      </c>
+      <c r="J19" t="n">
+        <v>9.640997023809524</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.67283163265306</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="S19" t="n">
+        <v>9.640997023809524</v>
+      </c>
+      <c r="T19" t="n">
+        <v>6.555431547619047</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>3.610491071428571</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.322172619047619</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="n">
+        <v>6.527118124448853</v>
       </c>
     </row>
     <row r="20">
@@ -1181,35 +1890,73 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.170434265318264</v>
+        <v>2733.219954648526</v>
       </c>
       <c r="D20" t="n">
-        <v>13.66623893307477</v>
+        <v>266.8170458362216</v>
       </c>
       <c r="E20" t="n">
-        <v>11.58338603450031</v>
+        <v>226.1518225783393</v>
       </c>
       <c r="F20" t="n">
         <v>1.179813820619534</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4824555469136346</v>
+        <v>0.4824555469136347</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5197217987804879</v>
+        <v>1.227678571428571</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5197217987804879</v>
+        <v>10.1469494047619</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5197217987804879</v>
+        <v>5.11780753968254</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4.125744047619047</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10.1469494047619</v>
+      </c>
+      <c r="T20" t="n">
+        <v>6.467633928571428</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>3.134300595238095</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.892485119047619</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.227678571428571</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="21">
@@ -1220,35 +1967,73 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.954788816180845</v>
+        <v>2651.020408163265</v>
       </c>
       <c r="D21" t="n">
-        <v>13.29865190750215</v>
+        <v>259.6403467655182</v>
       </c>
       <c r="E21" t="n">
-        <v>11.47990702128992</v>
+        <v>224.1315180347079</v>
       </c>
       <c r="F21" t="n">
         <v>1.15842853803949</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4941725002602364</v>
+        <v>0.4941725002602363</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5235327743902439</v>
+        <v>2.989211309523809</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5235327743902439</v>
+        <v>10.22135416666667</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5235327743902439</v>
+        <v>5.230422247023809</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>5.890997023809524</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10.22135416666667</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7.187965029761905</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.989211309523809</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.563988095238095</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.272879464285714</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>3.321314102564102</v>
       </c>
     </row>
     <row r="22">
@@ -1258,7 +2043,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="n">
+        <v>2.506643282312925</v>
       </c>
     </row>
     <row r="23">
@@ -1272,6 +2065,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>1.296037946428571</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1281,6 +2082,70 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>2.989211309523809</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="n">
+        <v>3.563988095238095</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <v>3.272879464285714</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/32/Filled_2D_sections/sagittal/week32_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/32/Filled_2D_sections/sagittal/week32_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2151,4 +2357,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week32_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2865.119047619047</v>
+      </c>
+      <c r="D10" t="n">
+        <v>67.94737403522794</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2651.020408163265</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2942.857142857143</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>275.83423579023</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13.62820562164837</v>
+      </c>
+      <c r="E11" t="n">
+        <v>259.6403467655182</v>
+      </c>
+      <c r="F11" t="n">
+        <v>307.8965814908345</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.161704629572267</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.03663910235031042</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.128112187130225</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.254313604449616</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.475914253753783</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0407136940631045</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3808962567791273</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.523707402600031</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0147.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0153.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0154.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0155.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0156.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0157.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0158.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0159.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0160.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0161.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0162.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0163.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0164.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.7591546545162482</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4103913408340617</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.136708081768532</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.273205651722827</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="n">
+        <v>12.99572172619047</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.1607649430102878</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12.82552083333333</v>
+      </c>
+      <c r="F48" t="n">
+        <v>13.203125</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>107</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.547306130396081</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.659385398728561</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.002976190476191</v>
+      </c>
+      <c r="F49" t="n">
+        <v>11.67596726190476</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>28</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.82140199829932</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.957820918392065</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.227678571428571</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.809523809523809</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>